--- a/diseases/d165/2000-2004.xlsx
+++ b/diseases/d165/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1545534886924321</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>13</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>9</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1738726747789861</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1352343026058781</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>10</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.05795755825966203</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.1352343026058781</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.09659593043277004</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>11</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2125110469520941</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>6</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -8925,9 +8880,6 @@
       <c r="O47" t="n">
         <v>6</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -9469,9 +9421,6 @@
       <c r="O50" t="n">
         <v>6</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1156521499445544</v>
       </c>
@@ -10013,9 +9962,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -10557,9 +10503,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -11101,9 +11044,6 @@
       <c r="O59" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>3</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.05782607497227721</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>7</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>5</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.09637679162046203</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>2</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.03855071664818481</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>5</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.09614375105998485</v>
       </c>
@@ -14365,9 +14290,6 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -14909,9 +14831,6 @@
       <c r="O80" t="n">
         <v>6</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1153725012719818</v>
       </c>
@@ -15453,9 +15372,6 @@
       <c r="O83" t="n">
         <v>6</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.1153725012719818</v>
       </c>
@@ -15997,9 +15913,6 @@
       <c r="O86" t="n">
         <v>2</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -16541,9 +16454,6 @@
       <c r="O89" t="n">
         <v>2</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -17085,9 +16995,6 @@
       <c r="O92" t="n">
         <v>4</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -17629,9 +17536,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -18173,9 +18077,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -18717,9 +18618,6 @@
       <c r="O101" t="n">
         <v>4</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.07691500084798789</v>
       </c>
@@ -19261,9 +19159,6 @@
       <c r="O104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -19805,9 +19700,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -20349,9 +20241,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O114" t="n">
         <v>5</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -21733,9 +21619,6 @@
       <c r="O118" t="n">
         <v>6</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -22425,9 +22308,6 @@
       <c r="O122" t="n">
         <v>5</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -23117,9 +22997,6 @@
       <c r="O126" t="n">
         <v>4</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -23809,9 +23686,6 @@
       <c r="O130" t="n">
         <v>3</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -24501,9 +24375,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -25193,9 +25064,6 @@
       <c r="O138" t="n">
         <v>4</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.07673191117130304</v>
       </c>
@@ -25885,9 +25753,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -26577,9 +26442,6 @@
       <c r="O146" t="n">
         <v>5</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -27269,9 +27131,6 @@
       <c r="O150" t="n">
         <v>3</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -27961,9 +27820,6 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.03836595558565152</v>
       </c>
@@ -28653,9 +28509,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -29345,9 +29198,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -30037,9 +29887,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -30729,9 +30576,6 @@
       <c r="O170" t="n">
         <v>4</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.07650892820937739</v>
       </c>
@@ -31421,9 +31265,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -32113,9 +31954,6 @@
       <c r="O178" t="n">
         <v>6</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.1147633923140661</v>
       </c>
@@ -32805,9 +32643,6 @@
       <c r="O182" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -33497,9 +33332,6 @@
       <c r="O186" t="n">
         <v>5</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -34189,9 +34021,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01912723205234435</v>
       </c>
@@ -34881,9 +34710,6 @@
       <c r="O194" t="n">
         <v>2</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -35573,9 +35399,6 @@
       <c r="O198" t="n">
         <v>3</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -36264,9 +36087,6 @@
       </c>
       <c r="O202" t="n">
         <v>1</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>0.01912723205234435</v>
